--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2021-06-01</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021-07-20</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2021-02-19</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-03-11</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2021-02-22</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2021-02-20</t>
+          <t>2021-02-21</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2021-02-23</t>
+          <t>2021-02-24</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2023-04-26</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2021-08-10</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2021-07-08</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2021-12-13</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2022-01-30</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2021-03-11</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2021-03-07</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2021-03-09</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
+          <t>2021-05-15</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12429,7 +12429,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>2021-03-17</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12863,7 +12863,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12925,7 +12925,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-08-31</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15157,7 +15157,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2021-03-03</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15777,7 +15777,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16397,7 +16397,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16707,7 +16707,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17575,7 +17575,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18071,7 +18071,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>2021-05-17</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18319,7 +18319,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18753,7 +18753,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19001,7 +19001,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>2021-02-08</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19125,7 +19125,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19497,7 +19497,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19621,7 +19621,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19745,7 +19745,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19869,7 +19869,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2021-02-24</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20551,7 +20551,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2021-02-04</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2021-02-17</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2024-02-11</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21295,7 +21295,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21543,7 +21543,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2021-01-20</t>
+          <t>2021-01-21</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-05</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21853,7 +21853,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2021-05-26</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22535,7 +22535,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2021-01-28</t>
+          <t>2021-01-29</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2021-02-01</t>
+          <t>2021-02-02</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23465,7 +23465,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23589,7 +23589,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23651,7 +23651,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2021-05-30</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23961,7 +23961,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24023,7 +24023,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24271,7 +24271,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24519,7 +24519,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2021-02-03</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2021-07-07</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2021-02-09</t>
+          <t>2021-02-10</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2021-01-17</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2021-02-16</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25077,7 +25077,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25325,7 +25325,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2021-02-10</t>
+          <t>2021-02-11</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2021-02-08</t>
+          <t>2021-02-09</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2021-02-16</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25626,7 +25626,7 @@
           <t>A | 1394呎 (4+房)
 $4928万
 $35,352/呎
-(21年-03月-04日)</t>
+(21年-03月-05日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -25635,7 +25635,7 @@
           <t>C | 552呎 (3房)
 $1454万
 $26,333/呎
-(21年-06月-15日)</t>
+(21年-06月-16日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -25643,7 +25643,7 @@
           <t>D | 470呎 (2房)
 $1261万
 $26,838/呎
-(21年-06月-01日)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -25651,7 +25651,7 @@
           <t>E | 674呎 (3房)
 $1794万
 $26,610/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -25659,7 +25659,7 @@
           <t>F | 353呎 (1房)
 $908万
 $25,731/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -25674,7 +25674,7 @@
           <t>A | 762呎 (3房)
 $2120万
 $27,822/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -25682,7 +25682,7 @@
           <t>B | 678呎 (3房)
 $1896万
 $27,972/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -25690,7 +25690,7 @@
           <t>C | 551呎 (3房)
 $1562万
 $28,347/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -25698,7 +25698,7 @@
           <t>D | 482呎 (2房)
 $1242万
 $25,776/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -25706,7 +25706,7 @@
           <t>E | 674呎 (3房)
 $1708万
 $25,337/呎
-(21年-03月-11日)</t>
+(21年-03月-12日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -25714,7 +25714,7 @@
           <t>F | 354呎 (1房)
 $908万
 $25,655/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
           <t>A | 762呎 (3房)
 $1954万
 $25,640/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -25737,7 +25737,7 @@
           <t>B | 678呎 (3房)
 $1800万
 $26,541/呎
-(21年-07月-19日)</t>
+(21年-07月-20日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -25745,7 +25745,7 @@
           <t>C | 551呎 (3房)
 $1467万
 $26,628/呎
-(21年-07月-22日)</t>
+(21年-07月-23日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -25753,7 +25753,7 @@
           <t>D | 482呎 (2房)
 $1258万
 $26,089/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -25761,7 +25761,7 @@
           <t>E | 674呎 (3房)
 $1761万
 $26,122/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -25769,7 +25769,7 @@
           <t>F | 353呎 (1房)
 $908万
 $25,725/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
           <t>A | 762呎 (3房)
 $2001万
 $26,260/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -25800,7 +25800,7 @@
           <t>C | 551呎 (3房)
 $1427万
 $25,897/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -25808,7 +25808,7 @@
           <t>D | 482呎 (2房)
 $1281万
 $26,575/呎
-(21年-03月-11日)</t>
+(21年-03月-12日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -25816,7 +25816,7 @@
           <t>E | 674呎 (3房)
 $1772万
 $26,294/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -25824,7 +25824,7 @@
           <t>F | 354呎 (1房)
 $903万
 $25,520/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
           <t>A | 762呎 (3房)
 $2082万
 $27,323/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -25847,7 +25847,7 @@
           <t>B | 678呎 (3房)
 $1958万
 $28,873/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -25855,7 +25855,7 @@
           <t>C | 551呎 (3房)
 $1424万
 $25,835/呎
-(21年-02月-18日)</t>
+(21年-02月-19日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -25863,7 +25863,7 @@
           <t>D | 482呎 (2房)
 $1281万
 $26,577/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -25871,7 +25871,7 @@
           <t>E | 674呎 (3房)
 $1767万
 $26,212/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -25879,7 +25879,7 @@
           <t>F | 354呎 (1房)
 $903万
 $25,517/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -25894,7 +25894,7 @@
           <t>A | 762呎 (3房)
 $1966万
 $25,801/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -25902,7 +25902,7 @@
           <t>B | 678呎 (3房)
 $1872万
 $27,611/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -25910,7 +25910,7 @@
           <t>C | 551呎 (3房)
 $1490万
 $27,038/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -25918,7 +25918,7 @@
           <t>D | 482呎 (2房)
 $1301万
 $26,992/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -25926,7 +25926,7 @@
           <t>E | 674呎 (3房)
 $1687万
 $25,036/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -25934,7 +25934,7 @@
           <t>F | 353呎 (1房)
 $906万
 $25,677/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -25949,7 +25949,7 @@
           <t>A | 762呎 (3房)
 $1944万
 $25,509/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>B | 678呎 (3房)
 $1861万
 $27,448/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>C | 551呎 (3房)
 $1485万
 $26,956/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -25973,7 +25973,7 @@
           <t>D | 482呎 (2房)
 $1278万
 $26,510/呎
-(21年-03月-10日)</t>
+(21年-03月-11日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -25981,7 +25981,7 @@
           <t>E | 674呎 (3房)
 $1722万
 $25,552/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -25989,7 +25989,7 @@
           <t>F | 353呎 (1房)
 $867万
 $24,555/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -26004,7 +26004,7 @@
           <t>A | 761呎 (3房)
 $1958万
 $25,729/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -26012,7 +26012,7 @@
           <t>B | 678呎 (3房)
 $1861万
 $27,445/呎
-(24年-04月-09日)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -26020,7 +26020,7 @@
           <t>C | 551呎 (3房)
 $1406万
 $25,523/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -26028,7 +26028,7 @@
           <t>D | 482呎 (2房)
 $1220万
 $25,315/呎
-(21年-03月-11日)</t>
+(21年-03月-12日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -26036,7 +26036,7 @@
           <t>E | 674呎 (3房)
 $1657万
 $24,586/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -26044,7 +26044,7 @@
           <t>F | 354呎 (1房)
 $866万
 $24,452/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -26059,7 +26059,7 @@
           <t>A | 762呎 (3房)
 $1928万
 $25,300/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -26067,7 +26067,7 @@
           <t>B | 678呎 (3房)
 $1855万
 $27,363/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -26075,7 +26075,7 @@
           <t>C | 551呎 (3房)
 $1442万
 $26,174/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -26083,7 +26083,7 @@
           <t>D | 482呎 (2房)
 $1217万
 $25,241/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -26091,7 +26091,7 @@
           <t>E | 674呎 (3房)
 $1750万
 $25,970/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -26099,7 +26099,7 @@
           <t>F | 354呎 (1房)
 $860万
 $24,294/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26114,7 +26114,7 @@
           <t>A | 761呎 (3房)
 $2024万
 $26,603/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -26122,7 +26122,7 @@
           <t>B | 678呎 (3房)
 $1906万
 $28,108/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -26130,7 +26130,7 @@
           <t>C | 551呎 (3房)
 $1377万
 $24,995/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -26138,7 +26138,7 @@
           <t>D | 482呎 (2房)
 $1248万
 $25,884/呎
-(21年-02月-22日)</t>
+(21年-02月-23日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -26146,7 +26146,7 @@
           <t>E | 674呎 (3房)
 $1741万
 $25,826/呎
-(21年-02月-23日)</t>
+(21年-02月-24日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -26154,7 +26154,7 @@
           <t>F | 354呎 (1房)
 $859万
 $24,257/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -26169,7 +26169,7 @@
           <t>A | 761呎 (3房)
 $1889万
 $24,819/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -26177,7 +26177,7 @@
           <t>B | 678呎 (3房)
 $1876万
 $27,662/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -26185,7 +26185,7 @@
           <t>C | 551呎 (3房)
 $1429万
 $25,940/呎
-(21年-03月-09日)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -26193,7 +26193,7 @@
           <t>D | 482呎 (2房)
 $1188万
 $24,656/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -26201,7 +26201,7 @@
           <t>E | 674呎 (3房)
 $1658万
 $24,598/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -26209,7 +26209,7 @@
           <t>F | 353呎 (1房)
 $898万
 $25,448/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -26224,7 +26224,7 @@
           <t>A | 761呎 (3房)
 $1989万
 $26,137/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -26232,7 +26232,7 @@
           <t>B | 678呎 (3房)
 $1838万
 $27,106/呎
-(24年-03月-25日)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -26240,7 +26240,7 @@
           <t>C | 551呎 (3房)
 $1358万
 $24,648/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -26248,7 +26248,7 @@
           <t>D | 482呎 (2房)
 $1237万
 $25,664/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -26256,7 +26256,7 @@
           <t>E | 674呎 (3房)
 $1704万
 $25,286/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -26264,7 +26264,7 @@
           <t>F | 353呎 (1房)
 $859万
 $24,337/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
           <t>A | 761呎 (3房)
 $1960万
 $25,757/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -26287,7 +26287,7 @@
           <t>B | 678呎 (3房)
 $1932万
 $28,497/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -26295,7 +26295,7 @@
           <t>C | 551呎 (3房)
 $1361万
 $24,699/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -26303,7 +26303,7 @@
           <t>D | 482呎 (2房)
 $1181万
 $24,508/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -26311,7 +26311,7 @@
           <t>E | 674呎 (3房)
 $1623万
 $24,086/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -26319,7 +26319,7 @@
           <t>F | 353呎 (1房)
 $889万
 $25,181/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26334,7 +26334,7 @@
           <t>A | 762呎 (3房)
 $1990万
 $26,109/呎
-(23年-05月-10日)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>B | 678呎 (3房)
 $1822万
 $26,876/呎
-(24年-04月-16日)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -26350,7 +26350,7 @@
           <t>C | 551呎 (3房)
 $1416万
 $25,708/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -26358,7 +26358,7 @@
           <t>D | 482呎 (2房)
 $1230万
 $25,510/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -26366,7 +26366,7 @@
           <t>E | 674呎 (3房)
 $1647万
 $24,432/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -26374,7 +26374,7 @@
           <t>F | 354呎 (1房)
 $850万
 $24,014/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
           <t>A | 762呎 (3房)
 $1902万
 $24,961/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -26397,7 +26397,7 @@
           <t>B | 678呎 (3房)
 $1795万
 $26,479/呎
-(21年-07月-27日)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -26405,7 +26405,7 @@
           <t>C | 551呎 (3房)
 $1412万
 $25,632/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -26413,7 +26413,7 @@
           <t>D | 482呎 (2房)
 $1226万
 $25,436/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -26421,7 +26421,7 @@
           <t>E | 674呎 (3房)
 $1710万
 $25,366/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -26429,7 +26429,7 @@
           <t>F | 353呎 (1房)
 $849万
 $24,048/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
           <t>A | 761呎 (3房)
 $1861万
 $24,451/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -26452,7 +26452,7 @@
           <t>B | 678呎 (3房)
 $1811万
 $26,715/呎
-(24年-03月-26日)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -26460,7 +26460,7 @@
           <t>C | 551呎 (3房)
 $1374万
 $24,938/呎
-(21年-02月-20日)</t>
+(21年-02月-21日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -26468,7 +26468,7 @@
           <t>D | 482呎 (2房)
 $1196万
 $24,822/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -26476,7 +26476,7 @@
           <t>E | 674呎 (3房)
 $1680万
 $24,921/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -26484,7 +26484,7 @@
           <t>F | 354呎 (1房)
 $848万
 $23,944/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
           <t>A | 762呎 (3房)
 $1855万
 $24,345/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>B | 678呎 (3房)
 $1806万
 $26,636/呎
-(23年-04月-26日)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -26515,7 +26515,7 @@
           <t>C | 551呎 (3房)
 $1393万
 $25,285/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -26523,7 +26523,7 @@
           <t>D | 482呎 (2房)
 $1192万
 $24,739/呎
-(21年-02月-23日)</t>
+(21年-02月-24日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -26531,7 +26531,7 @@
           <t>E | 674呎 (3房)
 $1604万
 $23,798/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -26539,7 +26539,7 @@
           <t>F | 353呎 (1房)
 $882万
 $24,994/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26554,7 +26554,7 @@
           <t>A | 761呎 (3房)
 $1850万
 $24,304/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -26562,7 +26562,7 @@
           <t>B | 678呎 (3房)
 $1737万
 $25,614/呎
-(21年-08月-10日)</t>
+(21年-08月-11日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -26570,7 +26570,7 @@
           <t>C | 551呎 (3房)
 $1406万
 $25,514/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -26578,7 +26578,7 @@
           <t>D | 482呎 (2房)
 $1219万
 $25,297/呎
-(21年-10月-03日)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -26586,7 +26586,7 @@
           <t>E | 674呎 (3房)
 $1599万
 $23,728/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -26594,7 +26594,7 @@
           <t>F | 354呎 (1房)
 $881万
 $24,884/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -26609,7 +26609,7 @@
           <t>A | 762呎 (3房)
 $1991万
 $26,127/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -26617,7 +26617,7 @@
           <t>B | 678呎 (3房)
 $1710万
 $25,224/呎
-(21年-07月-08日)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -26625,7 +26625,7 @@
           <t>C | 551呎 (3房)
 $1385万
 $25,134/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -26633,7 +26633,7 @@
           <t>D | 482呎 (2房)
 $1164万
 $24,160/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -26641,7 +26641,7 @@
           <t>E | 674呎 (3房)
 $1618万
 $24,006/呎
-(21年-01月-28日)</t>
+(21年-01月-29日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -26649,7 +26649,7 @@
           <t>F | 354呎 (1房)
 $837万
 $23,647/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -26664,7 +26664,7 @@
           <t>A | 761呎 (3房)
 $1865万
 $24,506/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -26672,7 +26672,7 @@
           <t>B | 678呎 (3房)
 $1721万
 $25,385/呎
-(22年-01月-30日)</t>
+(22年-01月-31日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -26680,7 +26680,7 @@
           <t>C | 551呎 (3房)
 $1385万
 $25,136/呎
-(21年-03月-11日)</t>
+(21年-03月-12日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -26688,7 +26688,7 @@
           <t>D | 482呎 (2房)
 $821万
 $17,037/呎
-(21年-12月-13日)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -26696,7 +26696,7 @@
           <t>E | 674呎 (3房)
 $1573万
 $23,341/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -26704,7 +26704,7 @@
           <t>F | 353呎 (1房)
 $832万
 $23,572/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -26719,7 +26719,7 @@
           <t>A | 762呎 (3房)
 $1765万
 $23,167/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>B | 678呎 (3房)
 $1695万
 $24,999/呎
-(21年-06月-06日)</t>
+(21年-06月-07日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>C | 551呎 (3房)
 $1353万
 $24,555/呎
-(21年-03月-11日)</t>
+(21年-03月-12日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>D | 482呎 (2房)
 $1174万
 $24,365/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>E | 674呎 (3房)
 $1568万
 $23,272/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>F | 354呎 (1房)
 $866万
 $24,475/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
           <t>A | 761呎 (3房)
 $1743万
 $22,899/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -26782,7 +26782,7 @@
           <t>B | 678呎 (3房)
 $1763万
 $26,007/呎
-(21年-07月-18日)</t>
+(21年-07月-19日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -26790,7 +26790,7 @@
           <t>C | 551呎 (3房)
 $1311万
 $23,789/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -26798,7 +26798,7 @@
           <t>D | 482呎 (2房)
 $1154万
 $23,952/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -26806,7 +26806,7 @@
           <t>E | 674呎 (3房)
 $1633万
 $24,224/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>F | 354呎 (1房)
 $864万
 $24,418/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -26829,7 +26829,7 @@
           <t>A | 762呎 (3房)
 $1737万
 $22,801/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -26837,7 +26837,7 @@
           <t>B | 678呎 (3房)
 $1685万
 $24,850/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -26845,7 +26845,7 @@
           <t>C | 551呎 (3房)
 $1323万
 $24,015/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -26853,7 +26853,7 @@
           <t>D | 482呎 (2房)
 $1167万
 $24,210/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -26861,7 +26861,7 @@
           <t>E | 674呎 (3房)
 $1559万
 $23,132/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -26869,7 +26869,7 @@
           <t>F | 354呎 (1房)
 $862万
 $24,345/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -26884,7 +26884,7 @@
           <t>A | 761呎 (3房)
 $1756万
 $23,076/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -26892,7 +26892,7 @@
           <t>B | 678呎 (3房)
 $1700万
 $25,081/呎
-(21年-12月-30日)</t>
+(21年-12月-31日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -26900,7 +26900,7 @@
           <t>C | 551呎 (3房)
 $1303万
 $23,646/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -26908,7 +26908,7 @@
           <t>D | 482呎 (2房)
 $1192万
 $24,734/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -26916,7 +26916,7 @@
           <t>E | 674呎 (3房)
 $1607万
 $23,849/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -26924,7 +26924,7 @@
           <t>F | 354呎 (1房)
 $859万
 $24,274/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -26939,7 +26939,7 @@
           <t>A | 762呎 (3房)
 $1762万
 $23,119/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -26947,7 +26947,7 @@
           <t>B | 678呎 (3房)
 $1727万
 $25,468/呎
-(22年-01月-17日)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -26955,7 +26955,7 @@
           <t>C | 551呎 (3房)
 $1356万
 $24,613/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -26963,7 +26963,7 @@
           <t>D | 482呎 (2房)
 $1147万
 $23,797/呎
-(21年-03月-04日)</t>
+(21年-03月-05日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -26971,7 +26971,7 @@
           <t>E | 674呎 (3房)
 $1574万
 $23,361/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -26979,7 +26979,7 @@
           <t>F | 354呎 (1房)
 $857万
 $24,201/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -26994,7 +26994,7 @@
           <t>A | 762呎 (3房)
 $1722万
 $22,597/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -27002,7 +27002,7 @@
           <t>B | 678呎 (3房)
 $1752万
 $25,848/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -27010,7 +27010,7 @@
           <t>C | 551呎 (3房)
 $1398万
 $25,367/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -27018,7 +27018,7 @@
           <t>D | 482呎 (2房)
 $1144万
 $23,726/呎
-(21年-03月-07日)</t>
+(21年-03月-08日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -27026,7 +27026,7 @@
           <t>E | 674呎 (3房)
 $1545万
 $22,924/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -27034,7 +27034,7 @@
           <t>F | 354呎 (1房)
 $858万
 $24,249/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -27049,7 +27049,7 @@
           <t>A | 762呎 (3房)
 $1783万
 $23,404/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -27057,7 +27057,7 @@
           <t>B | 678呎 (3房)
 $1685万
 $24,855/呎
-(21年-09月-06日)</t>
+(21年-09月-07日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -27065,7 +27065,7 @@
           <t>C | 551呎 (3房)
 $1311万
 $23,789/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -27073,7 +27073,7 @@
           <t>D | 482呎 (2房)
 $1143万
 $23,714/呎
-(21年-03月-09日)</t>
+(21年-03月-10日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -27081,7 +27081,7 @@
           <t>E | 674呎 (3房)
 $1540万
 $22,856/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -27089,7 +27089,7 @@
           <t>F | 354呎 (1房)
 $856万
 $24,178/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -27104,7 +27104,7 @@
           <t>A | 761呎 (3房)
 $1773万
 $23,296/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -27112,7 +27112,7 @@
           <t>B | 678呎 (3房)
 $1732万
 $25,544/呎
-(24年-03月-25日)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -27120,7 +27120,7 @@
           <t>C | 551呎 (3房)
 $1316万
 $23,882/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -27128,7 +27128,7 @@
           <t>D | 482呎 (2房)
 $1177万
 $24,427/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -27136,7 +27136,7 @@
           <t>E | 674呎 (3房)
 $1624万
 $24,098/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -27144,7 +27144,7 @@
           <t>F | 354呎 (1房)
 $807万
 $22,791/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27159,7 @@
           <t>A | 762呎 (3房)
 $1693万
 $22,217/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -27167,7 +27167,7 @@
           <t>B | 678呎 (3房)
 $1642万
 $24,215/呎
-(21年-05月-14日)</t>
+(21年-05月-15日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -27175,7 +27175,7 @@
           <t>C | 551呎 (3房)
 $1336万
 $24,247/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -27183,7 +27183,7 @@
           <t>D | 482呎 (2房)
 $1124万
 $23,328/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -27191,7 +27191,7 @@
           <t>E | 674呎 (3房)
 $1527万
 $22,653/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -27199,7 +27199,7 @@
           <t>F | 354呎 (1房)
 $794万
 $22,418/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -27214,7 +27214,7 @@
           <t>A | 761呎 (3房)
 $1889万
 $24,820/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -27222,7 +27222,7 @@
           <t>B | 678呎 (3房)
 $1718万
 $25,342/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -27230,7 +27230,7 @@
           <t>C | 551呎 (3房)
 $1276万
 $23,156/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -27238,7 +27238,7 @@
           <t>D | 482呎 (2房)
 $1121万
 $23,257/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -27246,7 +27246,7 @@
           <t>E | 674呎 (3房)
 $1589万
 $23,580/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -27254,7 +27254,7 @@
           <t>F | 354呎 (1房)
 $815万
 $23,034/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -27269,7 +27269,7 @@
           <t>A | 762呎 (3房)
 $1674万
 $21,975/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -27277,7 +27277,7 @@
           <t>B | 678呎 (3房)
 $1713万
 $25,265/呎
-(24年-04月-15日)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -27285,7 +27285,7 @@
           <t>C | 551呎 (3房)
 $1272万
 $23,085/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -27293,7 +27293,7 @@
           <t>D | 482呎 (2房)
 $1118万
 $23,189/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -27301,7 +27301,7 @@
           <t>E | 674呎 (3房)
 $1503万
 $22,295/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -27309,7 +27309,7 @@
           <t>F | 354呎 (1房)
 $766万
 $21,644/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -27465,7 +27465,7 @@
           <t>A | 727呎 (3房)
 $1927万
 $26,512/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -27473,7 +27473,7 @@
           <t>B | 480呎 (2房)
 $1287万
 $26,810/呎
-(21年-03月-16日)</t>
+(21年-03月-17日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -27481,7 +27481,7 @@
           <t>C | 347呎 (1房)
 $902万
 $25,986/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -27489,7 +27489,7 @@
           <t>D | 437呎 (2房)
 $1149万
 $26,288/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -27497,7 +27497,7 @@
           <t>E | 445呎 (2房)
 $1104万
 $24,809/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -27505,7 +27505,7 @@
           <t>F | 279呎 (开放式)
 $719万
 $25,785/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -27513,7 +27513,7 @@
           <t>G | 441呎 (2房)
 $1087万
 $24,649/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -27528,7 +27528,7 @@
           <t>A | 727呎 (3房)
 $1921万
 $26,421/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -27536,7 +27536,7 @@
           <t>B | 480呎 (2房)
 $1315万
 $27,394/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -27544,7 +27544,7 @@
           <t>C | 347呎 (1房)
 $901万
 $25,954/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -27552,7 +27552,7 @@
           <t>D | 437呎 (2房)
 $1094万
 $25,027/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -27560,7 +27560,7 @@
           <t>E | 445呎 (2房)
 $1098万
 $24,663/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -27568,7 +27568,7 @@
           <t>F | 279呎 (开放式)
 $718万
 $25,742/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -27576,7 +27576,7 @@
           <t>G | 441呎 (2房)
 $1103万
 $25,018/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
     </row>
@@ -27591,7 +27591,7 @@
           <t>A | 727呎 (3房)
 $1945万
 $26,757/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -27599,7 +27599,7 @@
           <t>B | 480呎 (2房)
 $1330万
 $27,712/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -27607,7 +27607,7 @@
           <t>C | 347呎 (1房)
 $900万
 $25,934/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -27615,7 +27615,7 @@
           <t>D | 437呎 (2房)
 $1090万
 $24,954/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -27623,7 +27623,7 @@
           <t>E | 445呎 (2房)
 $1166万
 $26,202/呎
-(23年-05月-10日)</t>
+(23年-05月-11日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -27631,7 +27631,7 @@
           <t>F | 279呎 (开放式)
 $704万
 $25,229/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -27639,7 +27639,7 @@
           <t>G | 441呎 (2房)
 $1051万
 $23,830/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -27654,7 +27654,7 @@
           <t>A | 727呎 (3房)
 $2006万
 $27,598/呎
-(21年-05月-31日)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -27662,7 +27662,7 @@
           <t>B | 480呎 (2房)
 $1246万
 $25,952/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -27670,7 +27670,7 @@
           <t>C | 347呎 (1房)
 $938万
 $27,043/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -27678,7 +27678,7 @@
           <t>D | 437呎 (2房)
 $1093万
 $25,002/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -27686,7 +27686,7 @@
           <t>E | 445呎 (2房)
 $1091万
 $24,515/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -27694,7 +27694,7 @@
           <t>F | 280呎 (开放式)
 $674万
 $24,075/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -27702,7 +27702,7 @@
           <t>G | 441呎 (2房)
 $1071万
 $24,295/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -27717,7 +27717,7 @@
           <t>A | 727呎 (3房)
 $2011万
 $27,667/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -27725,7 +27725,7 @@
           <t>B | 480呎 (2房)
 $1265万
 $26,362/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -27733,7 +27733,7 @@
           <t>C | 347呎 (1房)
 $937万
 $27,014/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -27741,7 +27741,7 @@
           <t>D | 437呎 (2房)
 $1154万
 $26,407/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -27749,7 +27749,7 @@
           <t>E | 445呎 (2房)
 $1088万
 $24,440/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -27757,7 +27757,7 @@
           <t>F | 279呎 (开放式)
 $688万
 $24,642/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -27765,7 +27765,7 @@
           <t>G | 441呎 (2房)
 $1088万
 $24,667/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27780,7 @@
           <t>A | 727呎 (3房)
 $1982万
 $27,257/呎
-(21年-08月-30日)</t>
+(21年-08月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -27788,7 +27788,7 @@
           <t>B | 480呎 (2房)
 $1248万
 $25,992/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -27804,7 +27804,7 @@
           <t>D | 437呎 (2房)
 $1097万
 $25,105/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -27812,7 +27812,7 @@
           <t>E | 445呎 (2房)
 $1149万
 $25,813/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -27820,7 +27820,7 @@
           <t>F | 279呎 (开放式)
 $707万
 $25,341/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -27828,7 +27828,7 @@
           <t>G | 441呎 (2房)
 $1039万
 $23,558/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -27843,7 +27843,7 @@
           <t>A | 727呎 (3房)
 $1940万
 $26,684/呎
-(21年-07月-27日)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -27851,7 +27851,7 @@
           <t>B | 480呎 (2房)
 $1295万
 $26,985/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -27859,7 +27859,7 @@
           <t>C | 347呎 (1房)
 $935万
 $26,951/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -27867,7 +27867,7 @@
           <t>D | 437呎 (2房)
 $1078万
 $24,657/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -27875,7 +27875,7 @@
           <t>E | 445呎 (2房)
 $1078万
 $24,234/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -27883,7 +27883,7 @@
           <t>F | 279呎 (开放式)
 $717万
 $25,713/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -27891,7 +27891,7 @@
           <t>G | 441呎 (2房)
 $1094万
 $24,816/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -27906,7 +27906,7 @@
           <t>A | 727呎 (3房)
 $1929万
 $26,536/呎
-(21年-07月-28日)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -27914,7 +27914,7 @@
           <t>B | 480呎 (2房)
 $1234万
 $25,708/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -27922,7 +27922,7 @@
           <t>C | 347呎 (1房)
 $934万
 $26,902/呎
-(21年-03月-02日)</t>
+(21年-03月-03日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -27930,7 +27930,7 @@
           <t>D | 437呎 (2房)
 $1101万
 $25,201/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -27938,7 +27938,7 @@
           <t>E | 445呎 (2房)
 $1102万
 $24,771/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -27946,7 +27946,7 @@
           <t>F | 280呎 (开放式)
 $673万
 $24,032/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -27954,7 +27954,7 @@
           <t>G | 441呎 (2房)
 $1078万
 $24,447/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -27969,7 +27969,7 @@
           <t>A | 727呎 (3房)
 $1900万
 $26,132/呎
-(21年-07月-11日)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -27977,7 +27977,7 @@
           <t>B | 480呎 (2房)
 $1230万
 $25,631/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -27985,7 +27985,7 @@
           <t>C | 347呎 (1房)
 $932万
 $26,847/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -27993,7 +27993,7 @@
           <t>D | 437呎 (2房)
 $1093万
 $25,005/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -28001,7 +28001,7 @@
           <t>E | 445呎 (2房)
 $1085万
 $24,391/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -28009,7 +28009,7 @@
           <t>F | 280呎 (开放式)
 $691万
 $24,682/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -28017,7 +28017,7 @@
           <t>G | 441呎 (2房)
 $1030万
 $23,347/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28032,7 +28032,7 @@
           <t>A | 727呎 (3房)
 $1871万
 $25,730/呎
-(21年-05月-19日)</t>
+(21年-05月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -28040,7 +28040,7 @@
           <t>B | 480呎 (2房)
 $1410万
 $29,369/呎
-(21年-07月-25日)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -28048,7 +28048,7 @@
           <t>C | 347呎 (1房)
 $890万
 $25,640/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -28056,7 +28056,7 @@
           <t>D | 437呎 (2房)
 $1073万
 $24,556/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -28064,7 +28064,7 @@
           <t>E | 445呎 (2房)
 $1116万
 $25,074/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -28072,7 +28072,7 @@
           <t>F | 279呎 (开放式)
 $672万
 $24,090/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -28080,7 +28080,7 @@
           <t>G | 441呎 (2房)
 $1026万
 $23,277/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28095,7 +28095,7 @@
           <t>A | 727呎 (3房)
 $1883万
 $25,900/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -28103,7 +28103,7 @@
           <t>B | 480呎 (2房)
 $1213万
 $25,273/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -28111,7 +28111,7 @@
           <t>C | 347呎 (1房)
 $924万
 $26,637/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -28119,7 +28119,7 @@
           <t>D | 437呎 (2房)
 $1088万
 $24,902/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -28127,7 +28127,7 @@
           <t>E | 445呎 (2房)
 $1109万
 $24,926/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -28135,7 +28135,7 @@
           <t>F | 279呎 (开放式)
 $709万
 $25,401/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -28143,7 +28143,7 @@
           <t>G | 441呎 (2房)
 $1015万
 $23,023/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -28158,7 +28158,7 @@
           <t>A | 727呎 (3房)
 $1877万
 $25,821/呎
-(21年-06月-20日)</t>
+(21年-06月-21日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -28166,7 +28166,7 @@
           <t>B | 480呎 (2房)
 $1210万
 $25,198/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -28174,7 +28174,7 @@
           <t>C | 347呎 (1房)
 $882万
 $25,424/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -28182,7 +28182,7 @@
           <t>D | 437呎 (2房)
 $1085万
 $24,826/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -28190,7 +28190,7 @@
           <t>E | 445呎 (2房)
 $1073万
 $24,103/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -28198,7 +28198,7 @@
           <t>F | 280呎 (开放式)
 $706万
 $25,232/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -28206,7 +28206,7 @@
           <t>G | 441呎 (2房)
 $1057万
 $23,964/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -28221,7 +28221,7 @@
           <t>A | 727呎 (3房)
 $1877万
 $25,824/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -28229,7 +28229,7 @@
           <t>B | 480呎 (2房)
 $1274万
 $26,544/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -28237,7 +28237,7 @@
           <t>C | 347呎 (1房)
 $900万
 $25,934/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -28245,7 +28245,7 @@
           <t>D | 437呎 (2房)
 $1087万
 $24,874/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -28253,7 +28253,7 @@
           <t>E | 445呎 (2房)
 $1069万
 $24,029/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -28261,7 +28261,7 @@
           <t>F | 280呎 (开放式)
 $695万
 $24,814/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -28269,7 +28269,7 @@
           <t>G | 441呎 (2房)
 $1009万
 $22,884/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28284,7 +28284,7 @@
           <t>A | 727呎 (3房)
 $1912万
 $26,304/呎
-(21年-05月-16日)</t>
+(21年-05月-17日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -28292,7 +28292,7 @@
           <t>B | 480呎 (2房)
 $1202万
 $25,046/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -28300,7 +28300,7 @@
           <t>C | 347呎 (1房)
 $893万
 $25,738/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -28308,7 +28308,7 @@
           <t>D | 437呎 (2房)
 $1057万
 $24,192/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -28316,7 +28316,7 @@
           <t>E | 445呎 (2房)
 $1099万
 $24,701/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -28324,7 +28324,7 @@
           <t>F | 279呎 (开放式)
 $677万
 $24,265/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -28332,7 +28332,7 @@
           <t>G | 441呎 (2房)
 $1006万
 $22,816/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28347,7 +28347,7 @@
           <t>A | 727呎 (3房)
 $1837万
 $25,271/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -28355,7 +28355,7 @@
           <t>B | 480呎 (2房)
 $1214万
 $25,285/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -28363,7 +28363,7 @@
           <t>C | 347呎 (1房)
 $861万
 $24,801/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -28371,7 +28371,7 @@
           <t>D | 437呎 (2房)
 $1054万
 $24,121/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -28379,7 +28379,7 @@
           <t>E | 445呎 (2房)
 $1050万
 $23,591/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -28387,7 +28387,7 @@
           <t>F | 280呎 (开放式)
 $663万
 $23,671/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -28395,7 +28395,7 @@
           <t>G | 441呎 (2房)
 $1028万
 $23,322/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -28410,7 +28410,7 @@
           <t>A | 727呎 (3房)
 $1884万
 $25,916/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>B | 480呎 (2房)
 $1185万
 $24,692/呎
-(21年-02月-07日)</t>
+(21年-02月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>C | 347呎 (1房)
 $898万
 $25,882/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>D | 437呎 (2房)
 $1051万
 $24,048/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -28442,7 +28442,7 @@
           <t>E | 445呎 (2房)
 $1093万
 $24,555/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -28450,7 +28450,7 @@
           <t>F | 280呎 (开放式)
 $669万
 $23,882/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -28458,7 +28458,7 @@
           <t>G | 441呎 (2房)
 $1000万
 $22,680/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28473,7 +28473,7 @@
           <t>A | 727呎 (3房)
 $1826万
 $25,121/呎
-(21年-05月-20日)</t>
+(21年-05月-21日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -28481,7 +28481,7 @@
           <t>B | 480呎 (2房)
 $1236万
 $25,758/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -28489,7 +28489,7 @@
           <t>C | 347呎 (1房)
 $859万
 $24,755/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -28497,7 +28497,7 @@
           <t>D | 437呎 (2房)
 $1095万
 $25,050/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -28505,7 +28505,7 @@
           <t>E | 445呎 (2房)
 $1044万
 $23,449/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -28513,7 +28513,7 @@
           <t>F | 280呎 (开放式)
 $667万
 $23,811/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -28521,7 +28521,7 @@
           <t>G | 441呎 (2房)
 $1041万
 $23,608/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
           <t>A | 727呎 (3房)
 $1901万
 $26,149/呎
-(21年-02月-24日)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -28544,7 +28544,7 @@
           <t>B | 480呎 (2房)
 $1240万
 $25,838/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -28552,7 +28552,7 @@
           <t>C | 347呎 (1房)
 $859万
 $24,749/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -28560,7 +28560,7 @@
           <t>D | 437呎 (2房)
 $1047万
 $23,952/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -28568,7 +28568,7 @@
           <t>E | 445呎 (2房)
 $1055万
 $23,701/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -28576,7 +28576,7 @@
           <t>F | 279呎 (开放式)
 $675万
 $24,208/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -28584,7 +28584,7 @@
           <t>G | 441呎 (2房)
 $994万
 $22,546/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28599,7 +28599,7 @@
           <t>A | 727呎 (3房)
 $1815万
 $24,971/呎
-(21年-05月-23日)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -28607,7 +28607,7 @@
           <t>B | 480呎 (2房)
 $1184万
 $24,675/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -28615,7 +28615,7 @@
           <t>C | 347呎 (1房)
 $896万
 $25,821/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -28623,7 +28623,7 @@
           <t>D | 437呎 (2房)
 $1079万
 $24,696/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -28631,7 +28631,7 @@
           <t>E | 445呎 (2房)
 $1058万
 $23,775/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -28639,7 +28639,7 @@
           <t>F | 279呎 (开放式)
 $673万
 $24,136/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -28647,7 +28647,7 @@
           <t>G | 441呎 (2房)
 $1035万
 $23,467/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28662,7 +28662,7 @@
           <t>A | 727呎 (3房)
 $1888万
 $25,970/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -28670,7 +28670,7 @@
           <t>B | 480呎 (2房)
 $1177万
 $24,527/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -28678,7 +28678,7 @@
           <t>C | 347呎 (1房)
 $896万
 $25,810/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -28686,7 +28686,7 @@
           <t>D | 437呎 (2房)
 $1028万
 $23,515/呎
-(21年-02月-17日)</t>
+(21年-02月-18日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -28694,7 +28694,7 @@
           <t>E | 445呎 (2房)
 $1071万
 $24,070/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -28702,7 +28702,7 @@
           <t>F | 279呎 (开放式)
 $669万
 $23,993/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -28710,7 +28710,7 @@
           <t>G | 441呎 (2房)
 $998万
 $22,626/呎
-(21年-02月-04日)</t>
+(21年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28725,7 +28725,7 @@
           <t>A | 727呎 (3房)
 $1878万
 $25,836/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -28733,7 +28733,7 @@
           <t>B | 480呎 (2房)
 $1174万
 $24,454/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -28741,7 +28741,7 @@
           <t>C | 347呎 (1房)
 $858万
 $24,712/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -28749,7 +28749,7 @@
           <t>D | 437呎 (2房)
 $1070万
 $24,476/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -28757,7 +28757,7 @@
           <t>E | 445呎 (2房)
 $1087万
 $24,429/呎
-(24年-02月-11日)</t>
+(24年-02月-12日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -28765,7 +28765,7 @@
           <t>F | 279呎 (开放式)
 $668万
 $23,932/呎
-(21年-02月-02日)</t>
+(21年-02月-03日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -28773,7 +28773,7 @@
           <t>G | 441呎 (2房)
 $985万
 $22,331/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -28788,7 +28788,7 @@
           <t>A | 727呎 (3房)
 $1794万
 $24,674/呎
-(21年-03月-04日)</t>
+(21年-03月-05日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -28796,7 +28796,7 @@
           <t>B | 480呎 (2房)
 $1222万
 $25,454/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -28804,7 +28804,7 @@
           <t>C | 347呎 (1房)
 $858万
 $24,712/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -28812,7 +28812,7 @@
           <t>D | 437呎 (2房)
 $1041万
 $23,815/呎
-(21年-01月-20日)</t>
+(21年-01月-21日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -28820,7 +28820,7 @@
           <t>E | 445呎 (2房)
 $1065万
 $23,926/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -28828,7 +28828,7 @@
           <t>F | 280呎 (开放式)
 $666万
 $23,775/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -28836,7 +28836,7 @@
           <t>G | 441呎 (2房)
 $982万
 $22,261/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -28851,7 +28851,7 @@
           <t>A | 727呎 (3房)
 $1834万
 $25,220/呎
-(21年-05月-26日)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -28859,7 +28859,7 @@
           <t>B | 480呎 (2房)
 $1157万
 $24,108/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -28867,7 +28867,7 @@
           <t>C | 347呎 (1房)
 $858万
 $24,726/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -28875,7 +28875,7 @@
           <t>D | 437呎 (2房)
 $1018万
 $23,304/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -28883,7 +28883,7 @@
           <t>E | 445呎 (2房)
 $1017万
 $22,847/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -28891,7 +28891,7 @@
           <t>F | 279呎 (开放式)
 $636万
 $22,785/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -28899,7 +28899,7 @@
           <t>G | 441呎 (2房)
 $1000万
 $22,664/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
           <t>A | 727呎 (3房)
 $1833万
 $25,208/呎
-(21年-02月-25日)</t>
+(21年-02月-26日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -28922,7 +28922,7 @@
           <t>B | 480呎 (2房)
 $1154万
 $24,035/呎
-(21年-02月-02日)</t>
+(21年-02月-03日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -28930,7 +28930,7 @@
           <t>C | 347呎 (1房)
 $896万
 $25,816/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -28938,7 +28938,7 @@
           <t>D | 437呎 (2房)
 $1055万
 $24,135/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -28946,7 +28946,7 @@
           <t>E | 445呎 (2房)
 $1014万
 $22,780/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -28954,7 +28954,7 @@
           <t>F | 280呎 (开放式)
 $662万
 $23,632/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -28962,7 +28962,7 @@
           <t>G | 441呎 (2房)
 $999万
 $22,660/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
           <t>A | 727呎 (3房)
 $1856万
 $25,530/呎
-(21年-01月-28日)</t>
+(21年-01月-29日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -28985,7 +28985,7 @@
           <t>B | 480呎 (2房)
 $1160万
 $24,162/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -28993,7 +28993,7 @@
           <t>C | 347呎 (1房)
 $896万
 $25,810/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -29001,7 +29001,7 @@
           <t>D | 437呎 (2房)
 $1052万
 $24,064/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -29009,7 +29009,7 @@
           <t>E | 445呎 (2房)
 $1011万
 $22,712/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -29017,7 +29017,7 @@
           <t>F | 280呎 (开放式)
 $660万
 $23,561/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -29025,7 +29025,7 @@
           <t>G | 441呎 (2房)
 $999万
 $22,653/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -29040,7 +29040,7 @@
           <t>A | 727呎 (3房)
 $1723万
 $23,702/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -29048,7 +29048,7 @@
           <t>B | 480呎 (2房)
 $1207万
 $25,150/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -29056,7 +29056,7 @@
           <t>C | 347呎 (1房)
 $895万
 $25,790/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -29064,7 +29064,7 @@
           <t>D | 437呎 (2房)
 $1027万
 $23,499/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -29072,7 +29072,7 @@
           <t>E | 445呎 (2房)
 $1008万
 $22,643/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -29080,7 +29080,7 @@
           <t>F | 280呎 (开放式)
 $658万
 $23,493/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -29088,7 +29088,7 @@
           <t>G | 441呎 (2房)
 $957万
 $21,696/呎
-(21年-02月-01日)</t>
+(21年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -29103,7 +29103,7 @@
           <t>A | 727呎 (3房)
 $1767万
 $24,308/呎
-(21年-05月-30日)</t>
+(21年-05月-31日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -29111,7 +29111,7 @@
           <t>B | 480呎 (2房)
 $1204万
 $25,075/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -29119,7 +29119,7 @@
           <t>C | 347呎 (1房)
 $894万
 $25,758/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -29127,7 +29127,7 @@
           <t>D | 437呎 (2房)
 $1051万
 $24,041/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -29135,7 +29135,7 @@
           <t>E | 445呎 (2房)
 $1049万
 $23,569/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -29143,7 +29143,7 @@
           <t>F | 280呎 (开放式)
 $628万
 $22,436/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -29151,7 +29151,7 @@
           <t>G | 441呎 (2房)
 $1017万
 $23,061/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -29166,7 +29166,7 @@
           <t>A | 727呎 (3房)
 $1779万
 $24,466/呎
-(21年-06月-09日)</t>
+(21年-06月-10日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -29174,7 +29174,7 @@
           <t>B | 480呎 (2房)
 $1146万
 $23,875/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -29182,7 +29182,7 @@
           <t>C | 347呎 (1房)
 $890万
 $25,646/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -29190,7 +29190,7 @@
           <t>D | 437呎 (2房)
 $1008万
 $23,062/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -29198,7 +29198,7 @@
           <t>E | 445呎 (2房)
 $1030万
 $23,148/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -29206,7 +29206,7 @@
           <t>F | 279呎 (开放式)
 $620万
 $22,240/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -29214,7 +29214,7 @@
           <t>G | 441呎 (2房)
 $998万
 $22,642/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -29229,7 +29229,7 @@
           <t>A | 727呎 (3房)
 $1773万
 $24,393/呎
-(21年-07月-07日)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -29237,7 +29237,7 @@
           <t>B | 480呎 (2房)
 $1183万
 $24,646/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -29245,7 +29245,7 @@
           <t>C | 347呎 (1房)
 $888万
 $25,594/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -29253,7 +29253,7 @@
           <t>D | 437呎 (2房)
 $992万
 $22,707/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -29261,7 +29261,7 @@
           <t>E | 445呎 (2房)
 $1040万
 $23,360/呎
-(21年-02月-02日)</t>
+(21年-02月-03日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -29269,7 +29269,7 @@
           <t>F | 279呎 (开放式)
 $615万
 $22,050/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -29277,7 +29277,7 @@
           <t>G | 441呎 (2房)
 $956万
 $21,685/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29292,7 @@
           <t>A | 727呎 (3房)
 $1698万
 $23,349/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -29300,7 +29300,7 @@
           <t>B | 480呎 (2房)
 $1180万
 $24,573/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -29308,7 +29308,7 @@
           <t>C | 347呎 (1房)
 $888万
 $25,576/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -29316,7 +29316,7 @@
           <t>D | 437呎 (2房)
 $1020万
 $23,352/呎
-(21年-02月-16日)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -29324,7 +29324,7 @@
           <t>E | 445呎 (2房)
 $1030万
 $23,148/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -29332,7 +29332,7 @@
           <t>F | 280呎 (开放式)
 $637万
 $22,743/呎
-(21年-01月-16日)</t>
+(21年-01月-17日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -29340,7 +29340,7 @@
           <t>G | 441呎 (2房)
 $986万
 $22,349/呎
-(21年-02月-09日)</t>
+(21年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -29358,7 +29358,7 @@
           <t>D | 437呎 (2房)
 $989万
 $22,629/呎
-(21年-02月-15日)</t>
+(21年-02月-16日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -29366,7 +29366,7 @@
           <t>E | 445呎 (2房)
 $1035万
 $23,267/呎
-(21年-02月-08日)</t>
+(21年-02月-09日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -29374,7 +29374,7 @@
           <t>F | 279呎 (开放式)
 $597万
 $21,384/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -29382,7 +29382,7 @@
           <t>G | 452呎 (2房)
 $959万
 $21,217/呎
-(21年-02月-10日)</t>
+(21年-02月-11日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -23146,7 +23146,7 @@
         </is>
       </c>
       <c r="E364" s="4" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>6578000</v>
       </c>
       <c r="I364" s="5" t="n">
-        <v>23493</v>
+        <v>23577</v>
       </c>
       <c r="J364" s="3" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>6578000</v>
       </c>
       <c r="L364" s="5" t="n">
-        <v>23493</v>
+        <v>23577</v>
       </c>
       <c r="M364" s="3" t="inlineStr">
         <is>
@@ -29077,9 +29077,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 280呎 (开放式)
+          <t>F | 279呎 (开放式)
 $658万
-$23,493/呎
+$23,577/呎
 (21年-02月-10日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>17617000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>23119</v>
+        <v>23150</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>17617000</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>23119</v>
+        <v>23150</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -26936,9 +26936,9 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 762呎 (3房)
+          <t>A | 761呎 (3房)
 $1762万
-$23,119/呎
+$23,150/呎
 (21年-01月-17日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-Monaco 第1期.xlsx
+++ b/web/files/九龙-启德-Monaco 第1期.xlsx
@@ -2062,38 +2062,30 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>20172000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>29752</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K24" s="5" t="n">
+        <v>20172000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>29752</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2094,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25554,7 +25546,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25564,7 +25556,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25787,12 +25779,12 @@
 (21年-02月-17日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 678呎 (3房)
-招标单位
--
-(在售)</t>
+$2017万
+$29,752/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
